--- a/FATURA2026.xlsx
+++ b/FATURA2026.xlsx
@@ -1847,7 +1847,7 @@
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G
-&amp;"Times New Roman,Kalın"&amp;K000000MUAYENE GÖZETİM MERKEZİ BAŞKANLIĞI
+&amp;B&amp;"Times New Roman"&amp;10&amp;K000000MUAYENE GÖZETİM MERKEZİ BAŞKANLIĞI
 ÖLÇÜ ALETLERİ FATURA DETAYI FORMU</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"Doküman Kodu: 15.01.39.FR.009         Yayın Tarihi: 26.03.2020         Revizyon Tarih/No: 27.01.2026/15
      Bu dokümanın güncelliği, elektronik ortamda TSE Doküman Yönetim Sisteminden takip edilmelidir.&amp;R&amp;P/&amp;N</oddFooter>

--- a/FATURA2026.xlsx
+++ b/FATURA2026.xlsx
@@ -1843,7 +1843,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="1.5748031496063" bottom="0.59055118110236204" header="0.118110236220472" footer="0.196850393700787"/>
+  <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="1.35433070866142" bottom="0.59055118110236204" header="0.118110236220472" footer="0.196850393700787"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G

--- a/FATURA2026.xlsx
+++ b/FATURA2026.xlsx
@@ -1843,7 +1843,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="1.35433070866142" bottom="0.59055118110236204" header="0.118110236220472" footer="0.196850393700787"/>
+  <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="1.5748031496063" bottom="0.59055118110236204" header="0.118110236220472" footer="0.196850393700787"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G
